--- a/Sumaco/Rasgos_2025_con_rasgos_calculados.xlsx
+++ b/Sumaco/Rasgos_2025_con_rasgos_calculados.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU46"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,6 +665,26 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>new_TreeID</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Leaf area (cm²)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
           <t>QC_flag_rasgos</t>
         </is>
       </c>
@@ -808,7 +828,19 @@
       <c r="AT2" t="n">
         <v>213.4059008879977</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3730</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1434.898</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -929,7 +961,19 @@
       <c r="AT3" t="n">
         <v>242.9553264604811</v>
       </c>
-      <c r="AU3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3733</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1747.557</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1028,7 +1072,19 @@
       <c r="AT4" t="n">
         <v>370.5801579128047</v>
       </c>
-      <c r="AU4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3735</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3603.677</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1141,7 +1197,19 @@
       <c r="AT5" t="n">
         <v>214.0950347036839</v>
       </c>
-      <c r="AU5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3732</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1171.743</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1278,7 +1346,19 @@
       <c r="AT6" t="n">
         <v>284.4036697247706</v>
       </c>
-      <c r="AU6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3729</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2218.98</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1395,7 +1475,19 @@
       <c r="AT7" t="n">
         <v>447.7475417333638</v>
       </c>
-      <c r="AU7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3734</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1620037.376</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1528,7 +1620,19 @@
       <c r="AT8" t="n">
         <v>233.078448031719</v>
       </c>
-      <c r="AU8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3728</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3414.817</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1661,7 +1765,19 @@
       <c r="AT9" t="n">
         <v>213.3364420610865</v>
       </c>
-      <c r="AU9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3719</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1062.862</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1799,6 +1915,10 @@
         <v>423.9290989660266</v>
       </c>
       <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1931,7 +2051,19 @@
       <c r="AT11" t="n">
         <v>183.030303030303</v>
       </c>
-      <c r="AU11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3723</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>912.658</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2064,7 +2196,19 @@
       <c r="AT12" t="n">
         <v>270.6392547381947</v>
       </c>
-      <c r="AU12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3712</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1957.672</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2201,7 +2345,19 @@
       <c r="AT13" t="n">
         <v>370.3825857519789</v>
       </c>
-      <c r="AU13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3711</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>701.386</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2334,7 +2490,19 @@
       <c r="AT14" t="n">
         <v>274.8670212765957</v>
       </c>
-      <c r="AU14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3714</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2144.144</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2471,7 +2639,19 @@
       <c r="AT15" t="n">
         <v>316.2875448186681</v>
       </c>
-      <c r="AU15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3716</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3499.007</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2608,7 +2788,19 @@
       <c r="AT16" t="n">
         <v>244.2539929879236</v>
       </c>
-      <c r="AU16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3715</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1104.325</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2742,6 +2934,10 @@
         <v>202.9685881946842</v>
       </c>
       <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2871,6 +3067,10 @@
         <v>247.9560707748627</v>
       </c>
       <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2995,7 +3195,19 @@
       <c r="AT19" t="n">
         <v>401.4006634721711</v>
       </c>
-      <c r="AU19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3696</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1598.213</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3142,7 +3354,19 @@
       <c r="AT20" t="n">
         <v>385.7478465152702</v>
       </c>
-      <c r="AU20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3694</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2236.346</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3269,7 +3493,19 @@
       <c r="AT21" t="n">
         <v>347.1681798530047</v>
       </c>
-      <c r="AU21" t="inlineStr"/>
+      <c r="AU21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3697</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1324.51</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3392,7 +3628,19 @@
       <c r="AT22" t="n">
         <v>409.3061224489796</v>
       </c>
-      <c r="AU22" t="inlineStr"/>
+      <c r="AU22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>3699</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1660.381</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3517,7 +3765,19 @@
       <c r="AT23" t="n">
         <v>240.6883545497407</v>
       </c>
-      <c r="AU23" t="inlineStr"/>
+      <c r="AU23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3705</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1043.485</v>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3662,7 +3922,19 @@
       <c r="AT24" t="n">
         <v>375.6440281030445</v>
       </c>
-      <c r="AU24" t="inlineStr"/>
+      <c r="AU24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3706</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1524.084</v>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3792,6 +4064,10 @@
         <v>250.6513809275664</v>
       </c>
       <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3890,7 +4166,19 @@
       <c r="AT26" t="n">
         <v>268.3808758537565</v>
       </c>
-      <c r="AU26" t="inlineStr"/>
+      <c r="AU26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>3703</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1081.156</v>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4015,7 +4303,19 @@
       <c r="AT27" t="n">
         <v>266.984505363528</v>
       </c>
-      <c r="AU27" t="inlineStr"/>
+      <c r="AU27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>3671</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1185.436</v>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4142,7 +4442,19 @@
       <c r="AT28" t="n">
         <v>211.2442177677618</v>
       </c>
-      <c r="AU28" t="inlineStr"/>
+      <c r="AU28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>3675</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>2978.351</v>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4271,7 +4583,19 @@
       <c r="AT29" t="n">
         <v>309.048178613396</v>
       </c>
-      <c r="AU29" t="inlineStr"/>
+      <c r="AU29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>3682</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>2074.518</v>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4396,7 +4720,19 @@
       <c r="AT30" t="n">
         <v>330.6245646621779</v>
       </c>
-      <c r="AU30" t="inlineStr"/>
+      <c r="AU30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>3678</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2683.6</v>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4525,7 +4861,19 @@
       <c r="AT31" t="n">
         <v>309.5024250044908</v>
       </c>
-      <c r="AU31" t="inlineStr"/>
+      <c r="AU31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>3669</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>3790.717</v>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4638,7 +4986,19 @@
       <c r="AT32" t="n">
         <v>213.128976286871</v>
       </c>
-      <c r="AU32" t="inlineStr"/>
+      <c r="AU32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>3683</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1014.924</v>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4763,7 +5123,19 @@
       <c r="AT33" t="n">
         <v>237.1343053007628</v>
       </c>
-      <c r="AU33" t="inlineStr"/>
+      <c r="AU33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>3661</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4435.019</v>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4862,7 +5234,19 @@
       <c r="AT34" t="n">
         <v>223.8700564971751</v>
       </c>
-      <c r="AU34" t="inlineStr"/>
+      <c r="AU34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>3665</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1699.935</v>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4981,7 +5365,19 @@
       <c r="AT35" t="n">
         <v>397.8494623655914</v>
       </c>
-      <c r="AU35" t="inlineStr"/>
+      <c r="AU35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>3745</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>547.772</v>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5104,7 +5500,19 @@
       <c r="AT36" t="n">
         <v>435.3246753246753</v>
       </c>
-      <c r="AU36" t="inlineStr"/>
+      <c r="AU36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>3746</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>5435</v>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5225,7 +5633,19 @@
       <c r="AT37" t="n">
         <v>370.8390646492434</v>
       </c>
-      <c r="AU37" t="inlineStr"/>
+      <c r="AU37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>3747</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1607.596</v>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5346,7 +5766,19 @@
       <c r="AT38" t="n">
         <v>524.1567026343929</v>
       </c>
-      <c r="AU38" t="inlineStr"/>
+      <c r="AU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>3740</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>3825.594</v>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5487,7 +5919,19 @@
       <c r="AT39" t="n">
         <v>418.7817258883249</v>
       </c>
-      <c r="AU39" t="inlineStr"/>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>3739</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>939.917</v>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5606,7 +6050,19 @@
       <c r="AT40" t="n">
         <v>413.7651821862348</v>
       </c>
-      <c r="AU40" t="inlineStr"/>
+      <c r="AU40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>3757</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1052.385</v>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5729,7 +6185,19 @@
       <c r="AT41" t="n">
         <v>464.446756850503</v>
       </c>
-      <c r="AU41" t="inlineStr"/>
+      <c r="AU41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>3763</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1522.716</v>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5854,7 +6322,19 @@
       <c r="AT42" t="n">
         <v>304.5084996304508</v>
       </c>
-      <c r="AU42" t="inlineStr"/>
+      <c r="AU42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>3761</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1798.148</v>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5995,7 +6475,19 @@
       <c r="AT43" t="n">
         <v>407.7694880370466</v>
       </c>
-      <c r="AU43" t="inlineStr"/>
+      <c r="AU43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>3769</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1087.928</v>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6109,6 +6601,10 @@
         <v>490.205223880597</v>
       </c>
       <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6249,7 +6745,19 @@
       <c r="AT45" t="n">
         <v>411.9170984455959</v>
       </c>
-      <c r="AU45" t="inlineStr"/>
+      <c r="AU45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>3770</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1318.897</v>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6358,7 +6866,19 @@
       <c r="AT46" t="n">
         <v>501.1320754716981</v>
       </c>
-      <c r="AU46" t="inlineStr"/>
+      <c r="AU46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>3766</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>614.413</v>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Sumaco/Rasgos_2025_con_rasgos_calculados.xlsx
+++ b/Sumaco/Rasgos_2025_con_rasgos_calculados.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,57 +1092,39 @@
           <t>SUM_09</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no ID</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3732</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
+        <v>3735</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Clusiaceae</t>
+          <t>Sapindaceae</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chrysochlamys</t>
+          <t>Allophylus</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>membranacea</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>38637</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>tree  (5cm≤dbh&lt;10cm)</t>
-        </is>
-      </c>
+          <t>sp</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
         <v>1</v>
       </c>
@@ -1150,37 +1132,41 @@
       <c r="W5" s="2" t="n">
         <v>45902</v>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.73</v>
+        <v>58.26</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.01</v>
+        <v>21.59</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.311</v>
+        <v>0.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.281</v>
+        <v>0.26</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.298</v>
+        <v>0.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.288</v>
+        <v>0.23</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1192,22 +1178,22 @@
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>0.3013333333333333</v>
+        <v>0.245</v>
       </c>
       <c r="AT5" t="n">
-        <v>214.0950347036839</v>
+        <v>370.5801579128047</v>
       </c>
       <c r="AU5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
         <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>3732</v>
+        <v>3735</v>
       </c>
       <c r="AX5" t="n">
-        <v>1171.743</v>
+        <v>2732.261</v>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
@@ -1223,7 +1209,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3729</v>
+        <v>3732</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -1233,17 +1219,17 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Clusiaceae</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Ficus</t>
+          <t>Chrysochlamys</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>quijosana</t>
+          <t>membranacea</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1271,9 +1257,7 @@
       <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" s="2" t="n">
         <v>45902</v>
       </c>
@@ -1282,81 +1266,59 @@
         <v>20</v>
       </c>
       <c r="Z6" t="n">
-        <v>43.6</v>
+        <v>18.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>sucia</t>
-        </is>
-      </c>
+        <v>4.01</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.151</v>
+        <v>0.311</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.188</v>
+        <v>0.281</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.186</v>
+        <v>0.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.183</v>
+        <v>0.298</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.570796326794897</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0.2864788975654116</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.2864788975654116</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>173.3333333333333</v>
-      </c>
+        <v>0.288</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>0.1703333333333333</v>
+        <v>0.3013333333333333</v>
       </c>
       <c r="AT6" t="n">
-        <v>284.4036697247706</v>
+        <v>214.0950347036839</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
         <v>9</v>
       </c>
       <c r="AW6" t="n">
-        <v>3729</v>
+        <v>3732</v>
       </c>
       <c r="AX6" t="n">
-        <v>2218.98</v>
+        <v>1171.743</v>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
@@ -1372,7 +1334,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3734</v>
+        <v>3729</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1382,17 +1344,17 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Allophylus</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>floribundus</t>
+          <t>quijosana</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -1420,72 +1382,92 @@
       <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
       <c r="W7" s="2" t="n">
         <v>45902</v>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
         <v>20</v>
       </c>
       <c r="Z7" t="n">
-        <v>43.73</v>
+        <v>43.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.58</v>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+        <v>12.4</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>sucia</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.19</v>
+        <v>0.151</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.16</v>
+        <v>0.188</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.15</v>
+        <v>0.186</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.2</v>
+        <v>0.183</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+        <v>0.154</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.570796326794897</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.2864788975654116</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.2864788975654116</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>173.3333333333333</v>
+      </c>
       <c r="AS7" t="n">
-        <v>0.1816666666666667</v>
+        <v>0.1703333333333333</v>
       </c>
       <c r="AT7" t="n">
-        <v>447.7475417333638</v>
+        <v>284.4036697247706</v>
       </c>
       <c r="AU7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>3734</v>
+        <v>3729</v>
       </c>
       <c r="AX7" t="n">
-        <v>1620037.376</v>
+        <v>2218.98</v>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
@@ -1501,7 +1483,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3728</v>
+        <v>3734</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -1511,17 +1493,17 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Solanaceae</t>
+          <t>Sapindaceae</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Solanum</t>
+          <t>Allophylus</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cf anisophyllum</t>
+          <t>floribundus</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1549,102 +1531,88 @@
       <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" s="2" t="n">
         <v>45902</v>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y8" t="n">
         <v>20</v>
       </c>
       <c r="Z8" t="n">
-        <v>35.31</v>
+        <v>43.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.23</v>
+        <v>19.58</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.175</v>
+        <v>0.18</v>
       </c>
       <c r="AE8" t="n">
         <v>0.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.137</v>
+        <v>0.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.187</v>
+        <v>0.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.184</v>
+        <v>0.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1.256637061435917</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.5490845536670389</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.5490845536670389</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>91.30434782608698</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>0.176</v>
+        <v>0.1816666666666667</v>
       </c>
       <c r="AT8" t="n">
-        <v>233.078448031719</v>
+        <v>447.7475417333638</v>
       </c>
       <c r="AU8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AV8" t="n">
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>3728</v>
+        <v>3734</v>
       </c>
       <c r="AX8" t="n">
-        <v>3414.817</v>
+        <v>1620037.376</v>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SUM_10</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>238</v>
+          <t>SUM_09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no ID</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>3719</v>
+        <v>3728</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -1654,24 +1622,26 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Clusiaceae</t>
+          <t>Solanaceae</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Chrysochlamys</t>
+          <t>Solanum</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>membranacea</t>
+          <t>cf anisophyllum</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>38638</v>
-      </c>
-      <c r="L9" t="n">
-        <v>14.00563499208679</v>
+        <v>38637</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>tree  (5cm≤dbh&lt;10cm)</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1682,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1694,102 +1664,100 @@
         <v>1</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
         <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>42.89</v>
+        <v>35.31</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>flor</t>
-        </is>
-      </c>
+        <v>8.23</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.38</v>
+        <v>0.175</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.4</v>
+        <v>0.137</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.37</v>
+        <v>0.187</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.39</v>
+        <v>0.184</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.37</v>
+        <v>0.183</v>
       </c>
       <c r="AJ9" t="n">
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.8835729338221293</v>
+        <v>1.256637061435917</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.5092958178940651</v>
+        <v>0.5490845536670389</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5092958178940651</v>
+        <v>0.5490845536670389</v>
       </c>
       <c r="AR9" t="n">
-        <v>162.2222222222222</v>
+        <v>91.30434782608698</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.3866666666666667</v>
+        <v>0.176</v>
       </c>
       <c r="AT9" t="n">
-        <v>213.3364420610865</v>
+        <v>233.078448031719</v>
       </c>
       <c r="AU9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>3719</v>
+        <v>3728</v>
       </c>
       <c r="AX9" t="n">
-        <v>1062.862</v>
+        <v>3414.817</v>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SUM_10</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>244</v>
+          <t>SUM_09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>no ID</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>3725</v>
+        <v>3728</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -1799,34 +1767,32 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Salicaceae</t>
+          <t>Solanaceae</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Casearia</t>
+          <t>Solanum</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>tachirensis</t>
+          <t>cf anisophyllum</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>38638</v>
-      </c>
-      <c r="L10" t="n">
-        <v>21.00845248813019</v>
+        <v>38637</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>tree  (5cm≤dbh&lt;10cm)</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -1843,81 +1809,85 @@
         <v>1</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>27.08</v>
+        <v>35.31</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>herbivoría</t>
-        </is>
-      </c>
+        <v>8.23</v>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.15</v>
+        <v>0.175</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.137</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.17</v>
+        <v>0.187</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.17</v>
+        <v>0.184</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.17</v>
+        <v>0.183</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AN10" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.374446785945534</v>
+        <v>1.256637061435917</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5020201633527213</v>
+        <v>0.5490845536670389</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.5020201633527213</v>
+        <v>0.5490845536670389</v>
       </c>
       <c r="AR10" t="n">
-        <v>134.7826086956522</v>
+        <v>91.30434782608698</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="AT10" t="n">
-        <v>423.9290989660266</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
+        <v>233.078448031719</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3728</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1398.307</v>
+      </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1927,10 +1897,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C11" t="n">
-        <v>3723</v>
+        <v>3719</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -1957,17 +1927,13 @@
         <v>38638</v>
       </c>
       <c r="L11" t="n">
-        <v>13.36901521971921</v>
+        <v>14.00563499208679</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -1991,77 +1957,81 @@
         <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>33</v>
+        <v>42.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+        <v>9.15</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>flor</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AL11" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.77</v>
+        <v>1.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.452986602285279</v>
+        <v>0.8835729338221293</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.5230605697290398</v>
+        <v>0.5092958178940651</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.5230605697290398</v>
+        <v>0.5092958178940651</v>
       </c>
       <c r="AR11" t="n">
-        <v>132.8947368421053</v>
+        <v>162.2222222222222</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.32</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="AT11" t="n">
-        <v>183.030303030303</v>
+        <v>213.3364420610865</v>
       </c>
       <c r="AU11" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>3723</v>
+        <v>3719</v>
       </c>
       <c r="AX11" t="n">
-        <v>912.658</v>
+        <v>1062.862</v>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
@@ -2072,10 +2042,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C12" t="n">
-        <v>3712</v>
+        <v>3725</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -2085,35 +2055,39 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metteniusaceae</t>
+          <t>Salicaceae</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Calatola</t>
+          <t>Casearia</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>costaricensis</t>
+          <t>tachirensis</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
         <v>38638</v>
       </c>
       <c r="L12" t="n">
-        <v>15.59718442300574</v>
+        <v>21.00845248813019</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -2132,81 +2106,81 @@
         <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>62.26</v>
+        <v>27.08</v>
       </c>
       <c r="AA12" t="n">
-        <v>16.85</v>
+        <v>11.48</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>liquenes, herbivoría</t>
+          <t>herbivoría</t>
         </is>
       </c>
       <c r="AC12" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="AJ12" t="n">
         <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.9424777960769379</v>
+        <v>1.374446785945534</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.5199061474335248</v>
+        <v>0.5020201633527213</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.5199061474335248</v>
+        <v>0.5020201633527213</v>
       </c>
       <c r="AR12" t="n">
-        <v>126.530612244898</v>
+        <v>134.7826086956522</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.1916666666666667</v>
+        <v>0.165</v>
       </c>
       <c r="AT12" t="n">
-        <v>270.6392547381947</v>
+        <v>423.9290989660266</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>3712</v>
+        <v>3725</v>
       </c>
       <c r="AX12" t="n">
-        <v>1957.672</v>
+        <v>1055.458</v>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
@@ -2217,10 +2191,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C13" t="n">
-        <v>3711</v>
+        <v>3723</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -2230,24 +2204,24 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Clusiaceae</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Myrcia</t>
+          <t>Chrysochlamys</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>aliena</t>
+          <t>membranacea</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
         <v>38638</v>
       </c>
       <c r="L13" t="n">
-        <v>10.1859163578813</v>
+        <v>13.36901521971921</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2255,14 +2229,14 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1806, 3345</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -2278,84 +2252,80 @@
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z13" t="n">
-        <v>30.32</v>
+        <v>33</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.23</v>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> + nutrientes</t>
-        </is>
-      </c>
+        <v>6.04</v>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AM13" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.610066234964769</v>
+        <v>1.452986602285279</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.6273033854548852</v>
+        <v>0.5230605697290398</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.6273033854548852</v>
+        <v>0.5230605697290398</v>
       </c>
       <c r="AR13" t="n">
-        <v>103.960396039604</v>
+        <v>132.8947368421053</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="AT13" t="n">
-        <v>370.3825857519789</v>
+        <v>183.030303030303</v>
       </c>
       <c r="AU13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV13" t="n">
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>3711</v>
+        <v>3723</v>
       </c>
       <c r="AX13" t="n">
-        <v>701.386</v>
+        <v>912.658</v>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
@@ -2366,10 +2336,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C14" t="n">
-        <v>3714</v>
+        <v>3723</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -2379,24 +2349,24 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Clusiaceae</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ficus</t>
+          <t>Chrysochlamys</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cuatrecasana</t>
+          <t>membranacea</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
         <v>38638</v>
       </c>
       <c r="L14" t="n">
-        <v>12.73239544735163</v>
+        <v>13.36901521971921</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2404,14 +2374,14 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2427,80 +2397,80 @@
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="n">
-        <v>75.2</v>
+        <v>33</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.67</v>
+        <v>6.04</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="AJ14" t="n">
         <v>1</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.98</v>
+        <v>1.77</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.256637061435917</v>
+        <v>1.452986602285279</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.3660563691113593</v>
+        <v>0.5230605697290398</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.3660563691113593</v>
+        <v>0.5230605697290398</v>
       </c>
       <c r="AR14" t="n">
-        <v>113.0434782608696</v>
+        <v>132.8947368421053</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.215</v>
+        <v>0.32</v>
       </c>
       <c r="AT14" t="n">
-        <v>274.8670212765957</v>
+        <v>183.030303030303</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AV14" t="n">
         <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>3714</v>
+        <v>3723</v>
       </c>
       <c r="AX14" t="n">
-        <v>2144.144</v>
+        <v>899.241</v>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
@@ -2511,10 +2481,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C15" t="n">
-        <v>3716</v>
+        <v>3712</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -2524,39 +2494,35 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sabiaceae</t>
+          <t>Metteniusaceae</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Meliosma</t>
+          <t>Calatola</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>frondosa</t>
+          <t>costaricensis</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
         <v>38638</v>
       </c>
       <c r="L15" t="n">
-        <v>15.91549430918953</v>
+        <v>15.59718442300574</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2572,84 +2538,84 @@
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>170.13</v>
+        <v>62.26</v>
       </c>
       <c r="AA15" t="n">
-        <v>53.81</v>
+        <v>16.85</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>infeccion</t>
+          <t>liquenes, herbivoría</t>
         </is>
       </c>
       <c r="AC15" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="AJ15" t="n">
         <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.13</v>
+        <v>1.11</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.01</v>
+        <v>0.49</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.727875959474386</v>
+        <v>0.9424777960769379</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.584532700082961</v>
+        <v>0.5199061474335248</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.584532700082961</v>
+        <v>0.5199061474335248</v>
       </c>
       <c r="AR15" t="n">
-        <v>110.8910891089109</v>
+        <v>126.530612244898</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.2616666666666667</v>
+        <v>0.1916666666666667</v>
       </c>
       <c r="AT15" t="n">
-        <v>316.2875448186681</v>
+        <v>270.6392547381947</v>
       </c>
       <c r="AU15" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
         <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>3716</v>
+        <v>3712</v>
       </c>
       <c r="AX15" t="n">
-        <v>3499.007</v>
+        <v>1957.672</v>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
@@ -2659,13 +2625,11 @@
           <t>SUM_10</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>no ID</t>
-        </is>
+      <c r="B16" t="n">
+        <v>249</v>
       </c>
       <c r="C16" t="n">
-        <v>3715</v>
+        <v>3711</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -2675,32 +2639,34 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Melastomataceae</t>
+          <t>Myrtaceae</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Miconia</t>
+          <t>Myrcia</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>aff glaucescens</t>
+          <t>aliena</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
         <v>38638</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>tree  (5cm≤dbh&lt;10cm)</t>
-        </is>
+      <c r="L16" t="n">
+        <v>10.1859163578813</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1806, 3345</t>
+        </is>
+      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -2721,84 +2687,84 @@
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>25.67</v>
+        <v>30.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.27</v>
+        <v>11.23</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>herbivoría</t>
+          <t xml:space="preserve"> + nutrientes</t>
         </is>
       </c>
       <c r="AC16" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.8</v>
+        <v>1.01</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.433351648200343</v>
+        <v>1.610066234964769</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5581324031715783</v>
+        <v>0.6273033854548852</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.5581324031715783</v>
+        <v>0.6273033854548852</v>
       </c>
       <c r="AR16" t="n">
-        <v>130</v>
+        <v>103.960396039604</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.1716666666666667</v>
+        <v>0.26</v>
       </c>
       <c r="AT16" t="n">
-        <v>244.2539929879236</v>
+        <v>370.3825857519789</v>
       </c>
       <c r="AU16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>3715</v>
+        <v>3711</v>
       </c>
       <c r="AX16" t="n">
-        <v>1104.325</v>
+        <v>701.386</v>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
@@ -2808,13 +2774,11 @@
           <t>SUM_10</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no ID</t>
-        </is>
+      <c r="B17" t="n">
+        <v>251</v>
       </c>
       <c r="C17" t="n">
-        <v>3708</v>
+        <v>3714</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -2824,32 +2788,34 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Solanaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Solanum</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>cf anisophyllum</t>
+          <t>cuatrecasana</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
         <v>38638</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>tree  (5cm≤dbh&lt;10cm)</t>
-        </is>
+      <c r="L17" t="n">
+        <v>12.73239544735163</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -2870,266 +2836,282 @@
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>28.97</v>
+        <v>75.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.88</v>
+        <v>20.67</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="AD17" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AG17" t="n">
         <v>0.22</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AH17" t="n">
         <v>0.23</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0.19</v>
-      </c>
       <c r="AI17" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AL17" t="n">
-        <v>7.9</v>
+        <v>6.4</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.93</v>
+        <v>0.98</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.55116137270996</v>
+        <v>1.256637061435917</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.4061472978142544</v>
+        <v>0.3660563691113593</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.4061472978142544</v>
+        <v>0.3660563691113593</v>
       </c>
       <c r="AR17" t="n">
-        <v>206.3492063492063</v>
+        <v>113.0434782608696</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.2</v>
+        <v>0.215</v>
       </c>
       <c r="AT17" t="n">
-        <v>202.9685881946842</v>
-      </c>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
+        <v>274.8670212765957</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3714</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2144.144</v>
+      </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUM_11</t>
+          <t>SUM_10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C18" t="n">
-        <v>3695</v>
+        <v>3716</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
+          <t>Sabiaceae</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Erythrina</t>
+          <t>Meliosma</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>edulis</t>
+          <t>frondosa</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>38815</v>
+        <v>38638</v>
       </c>
       <c r="L18" t="n">
-        <v>24.52</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>40675</v>
-      </c>
-      <c r="N18" t="n">
-        <v>26.19</v>
-      </c>
-      <c r="O18" t="n">
-        <v>14.5</v>
-      </c>
+        <v>15.91549430918953</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
       <c r="W18" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
         <v>6</v>
       </c>
       <c r="Z18" t="n">
-        <v>81.95</v>
+        <v>170.13</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.32</v>
+        <v>53.81</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>herbivoría</t>
+          <t>infeccion</t>
         </is>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
+        <v>0.26</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.727875959474386</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.584532700082961</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.584532700082961</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>110.8910891089109</v>
+      </c>
       <c r="AS18" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.2616666666666667</v>
       </c>
       <c r="AT18" t="n">
-        <v>247.9560707748627</v>
-      </c>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
+        <v>316.2875448186681</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3716</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3499.007</v>
+      </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SUM_11</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>260</v>
+          <t>SUM_10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>no ID</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>3696</v>
+        <v>3715</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Melastomataceae</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Eugenia</t>
+          <t>Miconia</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>sericifolia</t>
+          <t>aff glaucescens</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>38815</v>
-      </c>
-      <c r="L19" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>40675</v>
-      </c>
-      <c r="N19" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="O19" t="n">
-        <v>23.9</v>
-      </c>
+        <v>38638</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>tree  (5cm≤dbh&lt;10cm)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3140,7 +3122,9 @@
       <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
       <c r="W19" s="2" t="n">
         <v>45901</v>
       </c>
@@ -3149,132 +3133,140 @@
         <v>20</v>
       </c>
       <c r="Z19" t="n">
-        <v>27.13</v>
+        <v>25.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.89</v>
+        <v>6.27</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t xml:space="preserve">infeccion </t>
+          <t>herbivoría</t>
         </is>
       </c>
       <c r="AC19" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.258</v>
+        <v>0.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.237</v>
+        <v>0.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.294</v>
+        <v>0.17</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.303</v>
+        <v>0.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.245</v>
+        <v>0.16</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.433351648200343</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.5581324031715783</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.5581324031715783</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>130</v>
+      </c>
       <c r="AS19" t="n">
-        <v>0.264</v>
+        <v>0.1716666666666667</v>
       </c>
       <c r="AT19" t="n">
-        <v>401.4006634721711</v>
+        <v>244.2539929879236</v>
       </c>
       <c r="AU19" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>3696</v>
+        <v>3715</v>
       </c>
       <c r="AX19" t="n">
-        <v>1598.213</v>
+        <v>1104.325</v>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SUM_11</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>261</v>
+          <t>SUM_10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>no ID</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>3694</v>
+        <v>3708</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Annonaceae</t>
+          <t>Solanaceae</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Annona</t>
+          <t>Solanum</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>edulis</t>
+          <t>cf anisophyllum</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>38815</v>
-      </c>
-      <c r="L20" t="n">
-        <v>28.93</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>40675</v>
-      </c>
-      <c r="N20" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="O20" t="n">
-        <v>20.6</v>
-      </c>
+        <v>38638</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>tree  (5cm≤dbh&lt;10cm)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>3350</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
@@ -3287,84 +3279,80 @@
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>63.85</v>
+        <v>28.97</v>
       </c>
       <c r="AA20" t="n">
-        <v>24.63</v>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">infeccion </t>
-        </is>
-      </c>
+        <v>5.88</v>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.286</v>
+        <v>0.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.294</v>
+        <v>0.23</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.241</v>
+        <v>0.19</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.215</v>
+        <v>0.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.234</v>
+        <v>0.19</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.237</v>
+        <v>0.18</v>
       </c>
       <c r="AJ20" t="n">
         <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AL20" t="n">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.7</v>
+        <v>1.93</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.256637061435917</v>
+        <v>1.55116137270996</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.310352139029196</v>
+        <v>0.4061472978142544</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.310352139029196</v>
+        <v>0.4061472978142544</v>
       </c>
       <c r="AR20" t="n">
-        <v>79.48717948717947</v>
+        <v>206.3492063492063</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.2511666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>385.7478465152702</v>
+        <v>202.9685881946842</v>
       </c>
       <c r="AU20" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>3694</v>
+        <v>3708</v>
       </c>
       <c r="AX20" t="n">
-        <v>2236.346</v>
+        <v>1359.033</v>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
@@ -3375,10 +3363,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C21" t="n">
-        <v>3697</v>
+        <v>3695</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -3394,38 +3382,36 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ficus</t>
+          <t>Erythrina</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>americana</t>
+          <t>edulis</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L21" t="n">
-        <v>40.92</v>
+        <v>24.52</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N21" t="n">
-        <v>49.9746521243298</v>
+        <v>26.19</v>
       </c>
       <c r="O21" t="n">
-        <v>29.6</v>
+        <v>14.5</v>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>1824</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>1</v>
       </c>
@@ -3442,41 +3428,45 @@
       <c r="W21" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y21" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="n">
-        <v>46.26</v>
+        <v>81.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>16.06</v>
+        <v>20.32</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>flores y frutos</t>
+          <t>herbivoría</t>
         </is>
       </c>
       <c r="AC21" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.467</v>
+        <v>0.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.417</v>
+        <v>0.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.447</v>
+        <v>0.21</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.444</v>
+        <v>0.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.433</v>
+        <v>0.16</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.429</v>
+        <v>0.18</v>
       </c>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
@@ -3488,22 +3478,22 @@
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>0.4394999999999999</v>
+        <v>0.1866666666666667</v>
       </c>
       <c r="AT21" t="n">
-        <v>347.1681798530047</v>
+        <v>247.9560707748627</v>
       </c>
       <c r="AU21" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AV21" t="n">
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>3697</v>
+        <v>3695</v>
       </c>
       <c r="AX21" t="n">
-        <v>1324.51</v>
+        <v>3060.808</v>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
@@ -3514,10 +3504,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C22" t="n">
-        <v>3699</v>
+        <v>3696</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -3533,42 +3523,44 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
+          <t>Myrtaceae</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Alchornea</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Eugenia</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>sericifolia</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L22" t="n">
-        <v>108.5</v>
+        <v>16.82</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N22" t="n">
-        <v>108.5436711744998</v>
+        <v>19.86</v>
       </c>
       <c r="O22" t="n">
-        <v>33.3</v>
+        <v>23.9</v>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
-        <v>3352</v>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
@@ -3579,39 +3571,39 @@
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>61.25</v>
+        <v>27.13</v>
       </c>
       <c r="AA22" t="n">
-        <v>25.07</v>
+        <v>10.89</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>herbivoría, infeccion</t>
+          <t xml:space="preserve">infeccion </t>
         </is>
       </c>
       <c r="AC22" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.276</v>
+        <v>0.258</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.285</v>
+        <v>0.237</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.321</v>
+        <v>0.294</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.296</v>
+        <v>0.303</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.29</v>
+        <v>0.245</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.307</v>
+        <v>0.247</v>
       </c>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
@@ -3623,22 +3615,22 @@
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="n">
-        <v>0.2958333333333333</v>
+        <v>0.264</v>
       </c>
       <c r="AT22" t="n">
-        <v>409.3061224489796</v>
+        <v>401.4006634721711</v>
       </c>
       <c r="AU22" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="AV22" t="n">
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>3699</v>
+        <v>3696</v>
       </c>
       <c r="AX22" t="n">
-        <v>1660.381</v>
+        <v>1598.213</v>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
@@ -3649,10 +3641,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="C23" t="n">
-        <v>3705</v>
+        <v>3694</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -3668,36 +3660,38 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Clusiaceae</t>
+          <t>Annonaceae</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Chrysochlamys</t>
+          <t>Annona</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>membranacea</t>
+          <t>edulis</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L23" t="n">
-        <v>15.18</v>
+        <v>28.93</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N23" t="n">
-        <v>15.48</v>
+        <v>31.9</v>
       </c>
       <c r="O23" t="n">
-        <v>15.9</v>
+        <v>20.6</v>
       </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>3350</v>
+      </c>
       <c r="R23" t="n">
         <v>1</v>
       </c>
@@ -3710,7 +3704,9 @@
       <c r="U23" t="n">
         <v>1</v>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
       <c r="W23" s="2" t="n">
         <v>45901</v>
       </c>
@@ -3719,63 +3715,81 @@
         <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>42.42</v>
+        <v>63.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>10.21</v>
+        <v>24.63</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>ojo 21 hojas</t>
+          <t xml:space="preserve">infeccion </t>
         </is>
       </c>
       <c r="AC23" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.36</v>
+        <v>0.286</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.36</v>
+        <v>0.294</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.35</v>
+        <v>0.241</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.34</v>
+        <v>0.215</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.33</v>
+        <v>0.234</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
+        <v>0.237</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1.256637061435917</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.310352139029196</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.310352139029196</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>79.48717948717947</v>
+      </c>
       <c r="AS23" t="n">
-        <v>0.3383333333333333</v>
+        <v>0.2511666666666667</v>
       </c>
       <c r="AT23" t="n">
-        <v>240.6883545497407</v>
+        <v>385.7478465152702</v>
       </c>
       <c r="AU23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
         <v>11</v>
       </c>
       <c r="AW23" t="n">
-        <v>3705</v>
+        <v>3694</v>
       </c>
       <c r="AX23" t="n">
-        <v>1043.485</v>
+        <v>2236.346</v>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
@@ -3786,10 +3800,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C24" t="n">
-        <v>3706</v>
+        <v>3697</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -3805,36 +3819,38 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Eugenia</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>sericifolia</t>
+          <t>americana</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L24" t="n">
-        <v>15.4</v>
+        <v>40.92</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N24" t="n">
-        <v>15.68</v>
+        <v>49.9746521243298</v>
       </c>
       <c r="O24" t="n">
-        <v>14.2</v>
+        <v>29.6</v>
       </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>1824</v>
+      </c>
       <c r="R24" t="n">
         <v>1</v>
       </c>
@@ -3842,14 +3858,12 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>45901</v>
       </c>
@@ -3858,81 +3872,63 @@
         <v>20</v>
       </c>
       <c r="Z24" t="n">
-        <v>42.7</v>
+        <v>46.26</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.04</v>
+        <v>16.06</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>liquenes, infeccion</t>
+          <t>flores y frutos</t>
         </is>
       </c>
       <c r="AC24" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.259</v>
+        <v>0.467</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.246</v>
+        <v>0.417</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.23</v>
+        <v>0.447</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.238</v>
+        <v>0.444</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.243</v>
+        <v>0.433</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0.5890486225480862</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.6960376177885556</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.6960376177885556</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>73.17073170731707</v>
-      </c>
+        <v>0.429</v>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="n">
-        <v>0.2443333333333333</v>
+        <v>0.4394999999999999</v>
       </c>
       <c r="AT24" t="n">
-        <v>375.6440281030445</v>
+        <v>347.1681798530047</v>
       </c>
       <c r="AU24" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="AV24" t="n">
         <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>3706</v>
+        <v>3697</v>
       </c>
       <c r="AX24" t="n">
-        <v>1524.084</v>
+        <v>1324.51</v>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
@@ -3943,10 +3939,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C25" t="n">
-        <v>3707</v>
+        <v>3697</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
@@ -3962,44 +3958,46 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Allophylus</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>floribundus</t>
+          <t>americana</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L25" t="n">
-        <v>16.12</v>
+        <v>40.92</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N25" t="n">
-        <v>17.78</v>
+        <v>49.9746521243298</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>29.6</v>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>1824</v>
+      </c>
       <c r="R25" t="n">
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
@@ -4008,45 +4006,41 @@
       <c r="W25" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>38.38</v>
+        <v>46.26</v>
       </c>
       <c r="AA25" t="n">
-        <v>9.619999999999999</v>
+        <v>16.06</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>herbivoría</t>
+          <t>flores y frutos</t>
         </is>
       </c>
       <c r="AC25" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.166</v>
+        <v>0.467</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.159</v>
+        <v>0.417</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.198</v>
+        <v>0.447</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.191</v>
+        <v>0.444</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.19</v>
+        <v>0.433</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.188</v>
+        <v>0.429</v>
       </c>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
@@ -4058,15 +4052,23 @@
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
       <c r="AS25" t="n">
-        <v>0.182</v>
+        <v>0.4394999999999999</v>
       </c>
       <c r="AT25" t="n">
-        <v>250.6513809275664</v>
-      </c>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
+        <v>347.1681798530047</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>3697</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>847.491294</v>
+      </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4075,39 +4077,63 @@
           <t>SUM_11</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>268</v>
+      </c>
       <c r="C26" t="n">
-        <v>3703</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+        <v>3699</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Cannabaceae</t>
+          <t>Euphorbiaceae</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Trema</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>micranthum</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>Alchornea</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" s="2" t="n">
+        <v>38815</v>
+      </c>
+      <c r="L26" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>40675</v>
+      </c>
+      <c r="N26" t="n">
+        <v>108.5436711744998</v>
+      </c>
+      <c r="O26" t="n">
+        <v>33.3</v>
+      </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>3352</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
@@ -4120,36 +4146,36 @@
         <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>24.89</v>
+        <v>61.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>6.68</v>
+        <v>25.07</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>herbivoría</t>
+          <t>herbivoría, infeccion</t>
         </is>
       </c>
       <c r="AC26" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.208</v>
+        <v>0.276</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.21</v>
+        <v>0.285</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.237</v>
+        <v>0.321</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.227</v>
+        <v>0.296</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.182</v>
+        <v>0.29</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.23</v>
+        <v>0.307</v>
       </c>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
@@ -4161,36 +4187,36 @@
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="inlineStr"/>
       <c r="AS26" t="n">
-        <v>0.2156666666666667</v>
+        <v>0.2958333333333333</v>
       </c>
       <c r="AT26" t="n">
-        <v>268.3808758537565</v>
+        <v>409.3061224489796</v>
       </c>
       <c r="AU26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AV26" t="n">
         <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>3703</v>
+        <v>3699</v>
       </c>
       <c r="AX26" t="n">
-        <v>1081.156</v>
+        <v>1660.381</v>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUM_12</t>
+          <t>SUM_11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C27" t="n">
-        <v>3671</v>
+        <v>3705</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -4206,38 +4232,38 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Clusiaceae</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Ficus</t>
+          <t>Chrysochlamys</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>americana ssp. andicola</t>
+          <t>membranacea</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L27" t="n">
-        <v>196.078889889215</v>
+        <v>15.18</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N27" t="n">
-        <v>196.7155096358969</v>
+        <v>15.48</v>
       </c>
       <c r="O27" t="n">
-        <v>32</v>
+        <v>15.9</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -4250,43 +4276,43 @@
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="n">
-        <v>33.56</v>
+        <v>42.42</v>
       </c>
       <c r="AA27" t="n">
-        <v>8.960000000000001</v>
+        <v>10.21</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>infectadas</t>
+          <t>ojo 21 hojas</t>
         </is>
       </c>
       <c r="AC27" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0.33</v>
       </c>
-      <c r="AE27" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
         <v>0.29</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0.28</v>
       </c>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
@@ -4298,36 +4324,36 @@
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr"/>
       <c r="AS27" t="n">
-        <v>0.3116666666666667</v>
+        <v>0.3383333333333333</v>
       </c>
       <c r="AT27" t="n">
-        <v>266.984505363528</v>
+        <v>240.6883545497407</v>
       </c>
       <c r="AU27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW27" t="n">
-        <v>3671</v>
+        <v>3705</v>
       </c>
       <c r="AX27" t="n">
-        <v>1185.436</v>
+        <v>1043.485</v>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SUM_12</t>
+          <t>SUM_11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C28" t="n">
-        <v>3675</v>
+        <v>3706</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -4343,38 +4369,36 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>Myrtaceae</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Ocotea</t>
+          <t>Eugenia</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>oblonga</t>
+          <t>sericifolia</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L28" t="n">
-        <v>30.29</v>
+        <v>15.4</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N28" t="n">
-        <v>30.72</v>
+        <v>15.68</v>
       </c>
       <c r="O28" t="n">
-        <v>27.8</v>
+        <v>14.2</v>
       </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>1828</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>1</v>
       </c>
@@ -4382,91 +4406,111 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
       <c r="W28" s="2" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
         <v>20</v>
       </c>
       <c r="Z28" t="n">
-        <v>84.31</v>
+        <v>42.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>17.81</v>
+        <v>16.04</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>herbivoría</t>
+          <t>liquenes, infeccion</t>
         </is>
       </c>
       <c r="AC28" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.26</v>
+        <v>0.259</v>
       </c>
       <c r="AE28" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="AI28" t="n">
         <v>0.25</v>
       </c>
-      <c r="AF28" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
+      <c r="AJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0.5890486225480862</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.6960376177885556</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.6960376177885556</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>73.17073170731707</v>
+      </c>
       <c r="AS28" t="n">
-        <v>0.2433333333333333</v>
+        <v>0.2443333333333333</v>
       </c>
       <c r="AT28" t="n">
-        <v>211.2442177677618</v>
+        <v>375.6440281030445</v>
       </c>
       <c r="AU28" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>3675</v>
+        <v>3706</v>
       </c>
       <c r="AX28" t="n">
-        <v>2978.351</v>
+        <v>1524.084</v>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SUM_12</t>
+          <t>SUM_11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C29" t="n">
-        <v>3682</v>
+        <v>3707</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -4499,16 +4543,16 @@
         <v>38815</v>
       </c>
       <c r="L29" t="n">
-        <v>13.35</v>
+        <v>16.12</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N29" t="n">
-        <v>14.83</v>
+        <v>17.78</v>
       </c>
       <c r="O29" t="n">
-        <v>17.2</v>
+        <v>18</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -4516,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -4526,7 +4570,7 @@
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4534,39 +4578,39 @@
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z29" t="n">
-        <v>51.06</v>
+        <v>38.38</v>
       </c>
       <c r="AA29" t="n">
-        <v>15.78</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>algunos liquenes, infeccion</t>
+          <t>herbivoría</t>
         </is>
       </c>
       <c r="AC29" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.15</v>
+        <v>0.166</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.16</v>
+        <v>0.159</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.16</v>
+        <v>0.198</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.17</v>
+        <v>0.191</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.18</v>
+        <v>0.188</v>
       </c>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
@@ -4578,132 +4622,104 @@
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.182</v>
       </c>
       <c r="AT29" t="n">
-        <v>309.048178613396</v>
+        <v>250.6513809275664</v>
       </c>
       <c r="AU29" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW29" t="n">
-        <v>3682</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>2074.518</v>
-      </c>
+        <v>3707</v>
+      </c>
+      <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SUM_12</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>293</v>
-      </c>
+          <t>SUM_11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>3678</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
+        <v>3703</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Malvaceae</t>
+          <t>Cannabaceae</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Matisia</t>
+          <t>Trema</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>castano</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>38815</v>
-      </c>
-      <c r="L30" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>40675</v>
-      </c>
-      <c r="N30" t="n">
-        <v>26.93</v>
-      </c>
-      <c r="O30" t="n">
-        <v>19.3</v>
-      </c>
+          <t>micranthum</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
         <v>1</v>
       </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="n">
-        <v>43.07</v>
+        <v>24.89</v>
       </c>
       <c r="AA30" t="n">
-        <v>14.24</v>
+        <v>6.68</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>hojas no completas, liquenes, mucha herbivoría</t>
+          <t>herbivoría</t>
         </is>
       </c>
       <c r="AC30" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.13</v>
+        <v>0.208</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.14</v>
+        <v>0.237</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.14</v>
+        <v>0.227</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.15</v>
+        <v>0.182</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
@@ -4715,22 +4731,22 @@
       <c r="AQ30" t="inlineStr"/>
       <c r="AR30" t="inlineStr"/>
       <c r="AS30" t="n">
-        <v>0.1383333333333333</v>
+        <v>0.2156666666666667</v>
       </c>
       <c r="AT30" t="n">
-        <v>330.6245646621779</v>
+        <v>268.3808758537565</v>
       </c>
       <c r="AU30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV30" t="n">
         <v>11</v>
       </c>
-      <c r="AV30" t="n">
-        <v>12</v>
-      </c>
       <c r="AW30" t="n">
-        <v>3678</v>
+        <v>3703</v>
       </c>
       <c r="AX30" t="n">
-        <v>2683.6</v>
+        <v>1081.156</v>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
@@ -4741,10 +4757,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="C31" t="n">
-        <v>3669</v>
+        <v>3671</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -4760,44 +4776,44 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Allophylus</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>floribundus</t>
+          <t>americana ssp. andicola</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L31" t="n">
-        <v>11.04</v>
+        <v>196.078889889215</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N31" t="n">
-        <v>12.86</v>
+        <v>196.7155096358969</v>
       </c>
       <c r="O31" t="n">
-        <v>12.1</v>
+        <v>32</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
@@ -4806,45 +4822,41 @@
       <c r="W31" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Z31" t="n">
-        <v>55.67</v>
+        <v>33.56</v>
       </c>
       <c r="AA31" t="n">
-        <v>17.23</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>herbivoría</t>
+          <t>infectadas</t>
         </is>
       </c>
       <c r="AC31" s="2" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
@@ -4856,22 +4868,22 @@
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="n">
-        <v>0.255</v>
+        <v>0.3116666666666667</v>
       </c>
       <c r="AT31" t="n">
-        <v>309.5024250044908</v>
+        <v>266.984505363528</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>3669</v>
+        <v>3671</v>
       </c>
       <c r="AX31" t="n">
-        <v>3790.717</v>
+        <v>1185.436</v>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
@@ -4881,56 +4893,66 @@
           <t>SUM_12</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no ID</t>
-        </is>
+      <c r="B32" t="n">
+        <v>282</v>
       </c>
       <c r="C32" t="n">
-        <v>3683</v>
+        <v>3675</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Solanaceae</t>
+          <t>Lauraceae</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cestrum</t>
+          <t>Ocotea</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>megalophyllum</t>
+          <t>oblonga</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
-        <v>38639</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>tree  (5cm≤dbh&lt;10cm)</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+        <v>38815</v>
+      </c>
+      <c r="L32" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>40675</v>
+      </c>
+      <c r="N32" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="O32" t="n">
+        <v>27.8</v>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>1828</v>
+      </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
@@ -4944,23 +4966,27 @@
         <v>20</v>
       </c>
       <c r="Z32" t="n">
-        <v>34.58</v>
+        <v>84.31</v>
       </c>
       <c r="AA32" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="AB32" t="inlineStr"/>
+        <v>17.81</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>herbivoría</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AG32" t="n">
         <v>0.24</v>
@@ -4969,7 +4995,7 @@
         <v>0.23</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
@@ -4981,22 +5007,22 @@
       <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="inlineStr"/>
       <c r="AS32" t="n">
-        <v>0.2383333333333333</v>
+        <v>0.2433333333333333</v>
       </c>
       <c r="AT32" t="n">
-        <v>213.128976286871</v>
+        <v>211.2442177677618</v>
       </c>
       <c r="AU32" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AV32" t="n">
         <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>3683</v>
+        <v>3675</v>
       </c>
       <c r="AX32" t="n">
-        <v>1014.924</v>
+        <v>2978.351</v>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
@@ -5007,10 +5033,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="C33" t="n">
-        <v>3661</v>
+        <v>3682</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
@@ -5026,33 +5052,33 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
+          <t>Sapindaceae</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Alchornea</t>
+          <t>Allophylus</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>cf latifolia</t>
+          <t>floribundus</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
         <v>38815</v>
       </c>
       <c r="L33" t="n">
-        <v>14</v>
+        <v>13.35</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>40675</v>
       </c>
       <c r="N33" t="n">
-        <v>14.49</v>
+        <v>14.83</v>
       </c>
       <c r="O33" t="n">
-        <v>11.8</v>
+        <v>17.2</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
@@ -5063,7 +5089,7 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
@@ -5072,38 +5098,42 @@
       <c r="W33" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>103.57</v>
+        <v>51.06</v>
       </c>
       <c r="AA33" t="n">
-        <v>24.56</v>
+        <v>15.78</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>herbivoría</t>
+          <t>algunos liquenes, infeccion</t>
         </is>
       </c>
       <c r="AC33" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AH33" t="n">
         <v>0.18</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.19</v>
       </c>
       <c r="AI33" t="n">
         <v>0.18</v>
@@ -5118,22 +5148,22 @@
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr"/>
       <c r="AS33" t="n">
-        <v>0.1866666666666666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AT33" t="n">
-        <v>237.1343053007628</v>
+        <v>309.048178613396</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AV33" t="n">
         <v>12</v>
       </c>
       <c r="AW33" t="n">
-        <v>3661</v>
+        <v>3682</v>
       </c>
       <c r="AX33" t="n">
-        <v>4435.019</v>
+        <v>2074.518</v>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
@@ -5143,39 +5173,65 @@
           <t>SUM_12</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>293</v>
+      </c>
       <c r="C34" t="n">
-        <v>3665</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+        <v>3678</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Clusiaceae</t>
+          <t>Malvaceae</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Chrysochlamys</t>
+          <t>Matisia</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>membranacea</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+          <t>castano</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>38815</v>
+      </c>
+      <c r="L34" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>40675</v>
+      </c>
+      <c r="N34" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="O34" t="n">
+        <v>19.3</v>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
       <c r="U34" t="n">
         <v>1</v>
       </c>
@@ -5185,39 +5241,39 @@
       </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>28.32</v>
+        <v>43.07</v>
       </c>
       <c r="AA34" t="n">
-        <v>6.34</v>
+        <v>14.24</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>hojas sucias</t>
+          <t>hojas no completas, liquenes, mucha herbivoría</t>
         </is>
       </c>
       <c r="AC34" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.29</v>
+        <v>0.13</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
@@ -5229,36 +5285,36 @@
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="inlineStr"/>
       <c r="AS34" t="n">
-        <v>0.295</v>
+        <v>0.1383333333333333</v>
       </c>
       <c r="AT34" t="n">
-        <v>223.8700564971751</v>
+        <v>330.6245646621779</v>
       </c>
       <c r="AU34" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV34" t="n">
         <v>12</v>
       </c>
       <c r="AW34" t="n">
-        <v>3665</v>
+        <v>3678</v>
       </c>
       <c r="AX34" t="n">
-        <v>1699.935</v>
+        <v>2683.6</v>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUM_16</t>
+          <t>SUM_12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>380</v>
+        <v>305</v>
       </c>
       <c r="C35" t="n">
-        <v>3745</v>
+        <v>3669</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
@@ -5274,34 +5330,36 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Sapindaceae</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Eugenia</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Allophylus</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>floribundus</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="n">
-        <v>38814</v>
+        <v>38815</v>
       </c>
       <c r="L35" t="n">
-        <v>36.58</v>
+        <v>11.04</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>40674</v>
+        <v>40675</v>
       </c>
       <c r="N35" t="n">
-        <v>38.51549622320959</v>
+        <v>12.86</v>
       </c>
       <c r="O35" t="n">
-        <v>28.7</v>
+        <v>12.1</v>
       </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
-        <v>3428</v>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
         <v>1</v>
       </c>
@@ -5309,46 +5367,54 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
-        <v>45902</v>
-      </c>
-      <c r="X35" t="inlineStr"/>
+        <v>45900</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y35" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Z35" t="n">
-        <v>9.300000000000001</v>
+        <v>55.67</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB35" t="inlineStr"/>
+        <v>17.23</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>herbivoría</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="n">
-        <v>45903</v>
+        <v>45900</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
@@ -5360,115 +5426,105 @@
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="n">
-        <v>0.1566666666666667</v>
+        <v>0.255</v>
       </c>
       <c r="AT35" t="n">
-        <v>397.8494623655914</v>
+        <v>309.5024250044908</v>
       </c>
       <c r="AU35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AV35" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AW35" t="n">
-        <v>3745</v>
+        <v>3669</v>
       </c>
       <c r="AX35" t="n">
-        <v>547.772</v>
+        <v>3790.717</v>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUM_16</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>381</v>
+          <t>SUM_12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>no ID</t>
+        </is>
       </c>
       <c r="C36" t="n">
-        <v>3746</v>
+        <v>3683</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Burseraceae</t>
+          <t>Solanaceae</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Protium</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>Cestrum</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>megalophyllum</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="n">
-        <v>38814</v>
-      </c>
-      <c r="L36" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>40674</v>
-      </c>
-      <c r="N36" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="O36" t="n">
-        <v>18.4</v>
-      </c>
+        <v>38639</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>tree  (5cm≤dbh&lt;10cm)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
-        <v>1925</v>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
-        <v>45902</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+        <v>45900</v>
+      </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="n">
-        <v>154</v>
+        <v>34.58</v>
       </c>
       <c r="AA36" t="n">
-        <v>67.04000000000001</v>
+        <v>7.37</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" s="2" t="n">
-        <v>45903</v>
+        <v>45901</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AE36" t="n">
         <v>0.24</v>
@@ -5477,13 +5533,13 @@
         <v>0.23</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
@@ -5495,36 +5551,36 @@
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="n">
-        <v>0.24</v>
+        <v>0.2383333333333333</v>
       </c>
       <c r="AT36" t="n">
-        <v>435.3246753246753</v>
+        <v>213.128976286871</v>
       </c>
       <c r="AU36" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AV36" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AW36" t="n">
-        <v>3746</v>
+        <v>3683</v>
       </c>
       <c r="AX36" t="n">
-        <v>5435</v>
+        <v>1014.924</v>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUM_16</t>
+          <t>SUM_12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="C37" t="n">
-        <v>3747</v>
+        <v>3661</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -5540,33 +5596,33 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Euphorbiaceae</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Perebea</t>
+          <t>Alchornea</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>xanthochyma</t>
+          <t>cf latifolia</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>38814</v>
+        <v>38815</v>
       </c>
       <c r="L37" t="n">
-        <v>15.21</v>
+        <v>14</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>40674</v>
+        <v>40675</v>
       </c>
       <c r="N37" t="n">
-        <v>15.3</v>
+        <v>14.49</v>
       </c>
       <c r="O37" t="n">
-        <v>15.6</v>
+        <v>11.8</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
@@ -5574,49 +5630,53 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
-        <v>45902</v>
+        <v>45900</v>
       </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
         <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>36.35</v>
+        <v>103.57</v>
       </c>
       <c r="AA37" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="AB37" t="inlineStr"/>
+        <v>24.56</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>herbivoría</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="n">
-        <v>45903</v>
+        <v>45901</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.169</v>
+        <v>0.18</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.168</v>
+        <v>0.18</v>
       </c>
       <c r="AH37" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AI37" t="n">
         <v>0.18</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.15</v>
       </c>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
@@ -5628,128 +5688,106 @@
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr"/>
       <c r="AS37" t="n">
-        <v>0.1678333333333333</v>
+        <v>0.1866666666666666</v>
       </c>
       <c r="AT37" t="n">
-        <v>370.8390646492434</v>
+        <v>237.1343053007628</v>
       </c>
       <c r="AU37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV37" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AW37" t="n">
-        <v>3747</v>
+        <v>3661</v>
       </c>
       <c r="AX37" t="n">
-        <v>1607.596</v>
+        <v>4435.019</v>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUM_16</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>389</v>
-      </c>
+          <t>SUM_12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>3740</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
+        <v>3665</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Burseraceae</t>
+          <t>Clusiaceae</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Protium</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" s="2" t="n">
-        <v>38814</v>
-      </c>
-      <c r="L38" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>40674</v>
-      </c>
-      <c r="N38" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="O38" t="n">
-        <v>18.7</v>
-      </c>
+          <t>Chrysochlamys</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>membranacea</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
-        <v>45902</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+        <v>45900</v>
+      </c>
+      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Z38" t="n">
-        <v>102.87</v>
+        <v>28.32</v>
       </c>
       <c r="AA38" t="n">
-        <v>53.92</v>
-      </c>
-      <c r="AB38" t="inlineStr"/>
+        <v>6.34</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>hojas sucias</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="n">
-        <v>45903</v>
+        <v>45901</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
@@ -5761,22 +5799,22 @@
       <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr"/>
       <c r="AS38" t="n">
-        <v>0.245</v>
+        <v>0.295</v>
       </c>
       <c r="AT38" t="n">
-        <v>524.1567026343929</v>
+        <v>223.8700564971751</v>
       </c>
       <c r="AU38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AV38" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AW38" t="n">
-        <v>3740</v>
+        <v>3665</v>
       </c>
       <c r="AX38" t="n">
-        <v>3825.594</v>
+        <v>1699.935</v>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
@@ -5787,10 +5825,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="C39" t="n">
-        <v>3739</v>
+        <v>3745</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
@@ -5806,12 +5844,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
+          <t>Myrtaceae</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Inga</t>
+          <t>Eugenia</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5819,26 +5857,26 @@
         <v>38814</v>
       </c>
       <c r="L39" t="n">
-        <v>32.17</v>
+        <v>36.58</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>40674</v>
       </c>
       <c r="N39" t="n">
-        <v>34.66</v>
+        <v>38.51549622320959</v>
       </c>
       <c r="O39" t="n">
-        <v>26.3</v>
+        <v>28.7</v>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -5846,90 +5884,68 @@
       <c r="U39" t="n">
         <v>1</v>
       </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>45902</v>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="n">
-        <v>19.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA39" t="n">
-        <v>8.25</v>
+        <v>3.7</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.195</v>
+        <v>0.16</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0.8639379797371932</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.4977209129419272</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.4977209129419272</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>88.37209302325583</v>
-      </c>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
       <c r="AS39" t="n">
-        <v>0.2091666666666666</v>
+        <v>0.1566666666666667</v>
       </c>
       <c r="AT39" t="n">
-        <v>418.7817258883249</v>
+        <v>397.8494623655914</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV39" t="n">
         <v>16</v>
       </c>
       <c r="AW39" t="n">
-        <v>3739</v>
+        <v>3745</v>
       </c>
       <c r="AX39" t="n">
-        <v>939.917</v>
+        <v>547.772</v>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
@@ -5940,10 +5956,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="C40" t="n">
-        <v>3757</v>
+        <v>3746</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
@@ -5959,12 +5975,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>Burseraceae</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Cryptocarya</t>
+          <t>Protium</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5972,20 +5988,20 @@
         <v>38814</v>
       </c>
       <c r="L40" t="n">
-        <v>21.17</v>
+        <v>13.61</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>40674</v>
       </c>
       <c r="N40" t="n">
-        <v>23.63</v>
+        <v>15.02</v>
       </c>
       <c r="O40" t="n">
-        <v>23.6</v>
+        <v>18.4</v>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>1929.4785</v>
+        <v>1925</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -6003,37 +6019,41 @@
       <c r="W40" s="2" t="n">
         <v>45902</v>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y40" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="Z40" t="n">
-        <v>24.7</v>
+        <v>154</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.22</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="AF40" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.22</v>
       </c>
-      <c r="AG40" t="n">
-        <v>0.21</v>
-      </c>
       <c r="AH40" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
@@ -6045,36 +6065,36 @@
       <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="inlineStr"/>
       <c r="AS40" t="n">
-        <v>0.215</v>
+        <v>0.24</v>
       </c>
       <c r="AT40" t="n">
-        <v>413.7651821862348</v>
+        <v>435.3246753246753</v>
       </c>
       <c r="AU40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV40" t="n">
         <v>16</v>
       </c>
       <c r="AW40" t="n">
-        <v>3757</v>
+        <v>3746</v>
       </c>
       <c r="AX40" t="n">
-        <v>1052.385</v>
+        <v>5435</v>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SUM_18</t>
+          <t>SUM_16</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="C41" t="n">
-        <v>3763</v>
+        <v>3747</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
@@ -6090,85 +6110,83 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Inga</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>Perebea</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>xanthochyma</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="n">
-        <v>38816</v>
+        <v>38814</v>
       </c>
       <c r="L41" t="n">
-        <v>22.25</v>
+        <v>15.21</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>40674</v>
       </c>
       <c r="N41" t="n">
-        <v>22.34</v>
+        <v>15.3</v>
       </c>
       <c r="O41" t="n">
-        <v>18.5</v>
+        <v>15.6</v>
       </c>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
-        <v>3449</v>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
-        <v>45903</v>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+        <v>45902</v>
+      </c>
+      <c r="X41" t="inlineStr"/>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z41" t="n">
-        <v>28.83</v>
+        <v>36.35</v>
       </c>
       <c r="AA41" t="n">
-        <v>13.39</v>
+        <v>13.48</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.16</v>
+        <v>0.169</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="AF41" t="n">
         <v>0.17</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.16</v>
+        <v>0.168</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
@@ -6180,36 +6198,36 @@
       <c r="AQ41" t="inlineStr"/>
       <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="n">
-        <v>0.1633333333333334</v>
+        <v>0.1678333333333333</v>
       </c>
       <c r="AT41" t="n">
-        <v>464.446756850503</v>
+        <v>370.8390646492434</v>
       </c>
       <c r="AU41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV41" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW41" t="n">
-        <v>3763</v>
+        <v>3747</v>
       </c>
       <c r="AX41" t="n">
-        <v>1522.716</v>
+        <v>1607.596</v>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SUM_18</t>
+          <t>SUM_16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>431</v>
+        <v>389</v>
       </c>
       <c r="C42" t="n">
-        <v>3761</v>
+        <v>3740</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
@@ -6225,36 +6243,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Malpighiaceae</t>
+          <t>Burseraceae</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Bunchosia</t>
+          <t>Protium</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" s="2" t="n">
-        <v>38816</v>
+        <v>38814</v>
       </c>
       <c r="L42" t="n">
-        <v>23.51</v>
+        <v>19.34</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>40674</v>
       </c>
       <c r="N42" t="n">
-        <v>23.84</v>
+        <v>20.43</v>
       </c>
       <c r="O42" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>same as 3463</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
         <v>1</v>
       </c>
@@ -6269,43 +6283,43 @@
       </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
-        <v>45903</v>
-      </c>
-      <c r="X42" t="inlineStr"/>
+        <v>45902</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y42" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>40.59</v>
+        <v>102.87</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>ojo 18 hojas</t>
-        </is>
-      </c>
+        <v>53.92</v>
+      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AD42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AF42" t="n">
         <v>0.24</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.25</v>
       </c>
       <c r="AG42" t="n">
         <v>0.24</v>
       </c>
       <c r="AH42" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AI42" t="n">
         <v>0.24</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0.25</v>
       </c>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
@@ -6320,33 +6334,33 @@
         <v>0.245</v>
       </c>
       <c r="AT42" t="n">
-        <v>304.5084996304508</v>
+        <v>524.1567026343929</v>
       </c>
       <c r="AU42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW42" t="n">
-        <v>3761</v>
+        <v>3740</v>
       </c>
       <c r="AX42" t="n">
-        <v>1798.148</v>
+        <v>3825.594</v>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SUM_18</t>
+          <t>SUM_16</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="C43" t="n">
-        <v>3769</v>
+        <v>3739</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -6362,41 +6376,39 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Ocotea</t>
+          <t>Inga</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" s="2" t="n">
-        <v>38816</v>
+        <v>38814</v>
       </c>
       <c r="L43" t="n">
-        <v>14.51</v>
+        <v>32.17</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>40674</v>
       </c>
       <c r="N43" t="n">
-        <v>15.38</v>
+        <v>34.66</v>
       </c>
       <c r="O43" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> LAU, =#412 canelo negro yana ajua</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+        <v>26.3</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="n">
+        <v>3427</v>
+      </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
@@ -6408,98 +6420,100 @@
         <v>1</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>45903</v>
-      </c>
-      <c r="X43" t="inlineStr"/>
+        <v>45902</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y43" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Z43" t="n">
-        <v>38.87</v>
+        <v>19.7</v>
       </c>
       <c r="AA43" t="n">
-        <v>15.85</v>
+        <v>8.25</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.28</v>
+        <v>0.195</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AJ43" t="n">
         <v>1</v>
       </c>
-      <c r="AK43" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="AO43" t="n">
-        <v>0.6872233929727672</v>
+        <v>0.8639379797371932</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.5238471269767526</v>
+        <v>0.4977209129419272</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.5238471269767526</v>
+        <v>0.4977209129419272</v>
       </c>
       <c r="AR43" t="n">
-        <v>77.77777777777779</v>
+        <v>88.37209302325583</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2091666666666666</v>
       </c>
       <c r="AT43" t="n">
-        <v>407.7694880370466</v>
+        <v>418.7817258883249</v>
       </c>
       <c r="AU43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW43" t="n">
-        <v>3769</v>
+        <v>3739</v>
       </c>
       <c r="AX43" t="n">
-        <v>1087.928</v>
+        <v>939.917</v>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SUM_18</t>
+          <t>SUM_16</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>441</v>
+        <v>399</v>
       </c>
       <c r="C44" t="n">
-        <v>3767</v>
+        <v>3757</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
@@ -6515,33 +6529,33 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Lauraceae</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Cryptocarya</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" s="2" t="n">
-        <v>38816</v>
+        <v>38814</v>
       </c>
       <c r="L44" t="n">
-        <v>10.15</v>
+        <v>21.17</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>40674</v>
       </c>
       <c r="N44" t="n">
-        <v>12.44</v>
+        <v>23.63</v>
       </c>
       <c r="O44" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Guarango</t>
-        </is>
-      </c>
+        <v>23.6</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>3451</v>
+        <v>1929.4785</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -6557,36 +6571,40 @@
       </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
-        <v>45903</v>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+        <v>45902</v>
+      </c>
+      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="Z44" t="n">
-        <v>21.44</v>
+        <v>24.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>No se puede medir grosor</t>
-        </is>
-      </c>
+        <v>10.22</v>
+      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" s="2" t="n">
         <v>45903</v>
       </c>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
+      <c r="AD44" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.21</v>
+      </c>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
@@ -6596,14 +6614,24 @@
       <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="inlineStr"/>
       <c r="AR44" t="inlineStr"/>
-      <c r="AS44" t="inlineStr"/>
+      <c r="AS44" t="n">
+        <v>0.215</v>
+      </c>
       <c r="AT44" t="n">
-        <v>490.205223880597</v>
-      </c>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr"/>
-      <c r="AX44" t="inlineStr"/>
+        <v>413.7651821862348</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>3757</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1052.385</v>
+      </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -6612,150 +6640,132 @@
           <t>SUM_18</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no ID</t>
-        </is>
+      <c r="B45" t="n">
+        <v>427</v>
       </c>
       <c r="C45" t="n">
-        <v>3770</v>
+        <v>3763</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Aniba</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>coto</t>
-        </is>
-      </c>
+          <t>Inga</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" s="2" t="n">
-        <v>38644</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>tree  (5cm≤dbh&lt;10cm)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>LAU, Aniba, in p19 gesammelt</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
+        <v>38816</v>
+      </c>
+      <c r="L45" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>40674</v>
+      </c>
+      <c r="N45" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="O45" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>3449</v>
+      </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
         <v>1</v>
       </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>45903</v>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z45" t="n">
-        <v>42.46</v>
+        <v>28.83</v>
       </c>
       <c r="AA45" t="n">
-        <v>17.49</v>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>sucio, musgo, liquenes</t>
-        </is>
-      </c>
+        <v>13.39</v>
+      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0.4319689898685966</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0.5092958178940651</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0.5092958178940651</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>86.36363636363636</v>
-      </c>
+        <v>0.16</v>
+      </c>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
       <c r="AS45" t="n">
-        <v>0.245</v>
+        <v>0.1633333333333334</v>
       </c>
       <c r="AT45" t="n">
-        <v>411.9170984455959</v>
+        <v>464.446756850503</v>
       </c>
       <c r="AU45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV45" t="n">
         <v>18</v>
       </c>
       <c r="AW45" t="n">
-        <v>3770</v>
+        <v>3763</v>
       </c>
       <c r="AX45" t="n">
-        <v>1318.897</v>
+        <v>1522.716</v>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
@@ -6765,46 +6775,58 @@
           <t>SUM_18</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>no ID</t>
-        </is>
+      <c r="B46" t="n">
+        <v>431</v>
       </c>
       <c r="C46" t="n">
-        <v>3766</v>
+        <v>3761</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Malpighiaceae</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Bunchosia</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" s="2" t="n">
-        <v>38644</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>tree  (5cm≤dbh&lt;10cm)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>LAU, kl. Blätter</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+        <v>38816</v>
+      </c>
+      <c r="L46" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>40674</v>
+      </c>
+      <c r="N46" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="O46" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>same as 3463</t>
+        </is>
+      </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -6821,35 +6843,39 @@
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z46" t="n">
-        <v>13.25</v>
+        <v>40.59</v>
       </c>
       <c r="AA46" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="AB46" t="inlineStr"/>
+        <v>12.36</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>ojo 18 hojas</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
@@ -6861,24 +6887,574 @@
       <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="n">
-        <v>0.175</v>
+        <v>0.245</v>
       </c>
       <c r="AT46" t="n">
-        <v>501.1320754716981</v>
+        <v>304.5084996304508</v>
       </c>
       <c r="AU46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV46" t="n">
         <v>18</v>
       </c>
       <c r="AW46" t="n">
+        <v>3761</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1798.148</v>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SUM_18</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>440</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3769</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Ocotea</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" s="2" t="n">
+        <v>38816</v>
+      </c>
+      <c r="L47" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>40674</v>
+      </c>
+      <c r="N47" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="O47" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> LAU, =#412 canelo negro yana ajua</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0.6872233929727672</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0.5238471269767526</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0.5238471269767526</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>407.7694880370466</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>3769</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1087.928</v>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SUM_18</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>441</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3767</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Fabaceae</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" s="2" t="n">
+        <v>38816</v>
+      </c>
+      <c r="L48" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>40674</v>
+      </c>
+      <c r="N48" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="O48" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Guarango</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>3451</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y48" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>No se puede medir grosor</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>490.205223880597</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>3767</v>
+      </c>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SUM_18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>no ID</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3770</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Aniba</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>coto</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>38644</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>tree  (5cm≤dbh&lt;10cm)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>LAU, Aniba, in p19 gesammelt</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>sucio, musgo, liquenes</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0.4319689898685966</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0.5092958178940651</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0.5092958178940651</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>86.36363636363636</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>411.9170984455959</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>3770</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1318.897</v>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SUM_18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>no ID</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
         <v>3766</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" s="2" t="n">
+        <v>38644</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>tree  (5cm≤dbh&lt;10cm)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>LAU, kl. Blätter</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>501.1320754716981</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>3766</v>
+      </c>
+      <c r="AX50" t="n">
         <v>614.413</v>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
